--- a/Assets/Scripts/Core/Parser/Monster.xlsx
+++ b/Assets/Scripts/Core/Parser/Monster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\OneDrive\바탕 화면\Dev\IdleGameProject\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EA5D7D-87A4-4AA3-A0A6-9EDA6F419A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0C4ADD-40B5-428B-BADF-373A423E043E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5295" yWindow="2085" windowWidth="13695" windowHeight="12645" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
+    <workbookView xWindow="2685" yWindow="1890" windowWidth="18210" windowHeight="12645" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>fileName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -65,6 +65,14 @@
   </si>
   <si>
     <t>HittedVFX,HittedVFX2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_ORC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HittedVFX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -521,6 +529,21 @@
         <v>7</v>
       </c>
     </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
+        <v>4294967299</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C5" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>

--- a/Assets/Scripts/Core/Parser/Monster.xlsx
+++ b/Assets/Scripts/Core/Parser/Monster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\OneDrive\바탕 화면\Dev\IdleGameProject\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Desktop\Dev\IdleRPG\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0C4ADD-40B5-428B-BADF-373A423E043E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E77C0C5-C4C1-45F9-AA1A-A795E57D9DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="1890" windowWidth="18210" windowHeight="12645" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
+    <workbookView xWindow="29580" yWindow="1215" windowWidth="21600" windowHeight="11295" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>fileName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -73,6 +73,46 @@
   </si>
   <si>
     <t>HittedVFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스켈레톤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropTable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -167,10 +207,17 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A1B23A3-760F-4789-9565-7F0577486AF3}" name="표3" displayName="표3" ref="D1:D101" totalsRowShown="0">
-  <autoFilter ref="D1:D101" xr:uid="{6A1B23A3-760F-4789-9565-7F0577486AF3}"/>
-  <tableColumns count="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A1B23A3-760F-4789-9565-7F0577486AF3}" name="표3" displayName="표3" ref="D1:K101" totalsRowShown="0">
+  <autoFilter ref="D1:K101" xr:uid="{6A1B23A3-760F-4789-9565-7F0577486AF3}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{CFEADB9E-09E3-4FA0-9B5D-075D597E2670}" name="VFX"/>
+    <tableColumn id="2" xr3:uid="{5B81A1E1-20BA-4AA3-B3B0-B0C84FF9F350}" name="Name"/>
+    <tableColumn id="3" xr3:uid="{A1D4EF20-200A-4B6E-A5A2-2C908927426C}" name="Hp"/>
+    <tableColumn id="4" xr3:uid="{21E81982-EE18-4BE9-9C47-E7FE997BA4AD}" name="Atk"/>
+    <tableColumn id="5" xr3:uid="{08F167D4-9378-4F5F-8839-8A2ED136CDF3}" name="Exp"/>
+    <tableColumn id="6" xr3:uid="{804B8966-2553-4634-9592-08D58A9FBB68}" name="MoveSpeed"/>
+    <tableColumn id="7" xr3:uid="{833B2309-2896-44C7-A7AC-ADC0A76FF064}" name="AttackSpeed"/>
+    <tableColumn id="8" xr3:uid="{664D9F71-D140-4871-A46A-78CC50DA2116}" name="DropTable"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -473,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330BEF0F-C7BC-4B2B-8199-B4DC333AF275}">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.25" customWidth="1"/>
@@ -483,9 +530,11 @@
     <col min="5" max="5" width="17.875" customWidth="1"/>
     <col min="6" max="6" width="14.75" customWidth="1"/>
     <col min="7" max="7" width="14.125" customWidth="1"/>
+    <col min="9" max="9" width="15.5" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,8 +547,29 @@
       <c r="D1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -513,8 +583,29 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -528,8 +619,29 @@
       <c r="D3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3">
+        <v>50</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -543,74 +655,95 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
+        <v>20</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4">
+        <v>1.5</v>
+      </c>
+      <c r="J4">
+        <v>0.8</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C5" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C6" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C7" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C8" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C9" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C10" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C11" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C12" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C13" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C14" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C15" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C16" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>

--- a/Assets/Scripts/Core/Parser/Monster.xlsx
+++ b/Assets/Scripts/Core/Parser/Monster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Desktop\Dev\IdleRPG\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E77C0C5-C4C1-45F9-AA1A-A795E57D9DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0E46A8-94CE-4EC1-AC19-805265F5AF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="1215" windowWidth="21600" windowHeight="11295" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
+    <workbookView xWindow="29190" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>fileName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -113,6 +113,14 @@
   </si>
   <si>
     <t>DropTable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrcHit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -207,10 +215,11 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A1B23A3-760F-4789-9565-7F0577486AF3}" name="표3" displayName="표3" ref="D1:K101" totalsRowShown="0">
-  <autoFilter ref="D1:K101" xr:uid="{6A1B23A3-760F-4789-9565-7F0577486AF3}"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A1B23A3-760F-4789-9565-7F0577486AF3}" name="표3" displayName="표3" ref="D1:L101" totalsRowShown="0">
+  <autoFilter ref="D1:L101" xr:uid="{6A1B23A3-760F-4789-9565-7F0577486AF3}"/>
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{CFEADB9E-09E3-4FA0-9B5D-075D597E2670}" name="VFX"/>
+    <tableColumn id="9" xr3:uid="{C782D7CA-7F20-4536-B9EB-2D19C533B1AF}" name="SFX"/>
     <tableColumn id="2" xr3:uid="{5B81A1E1-20BA-4AA3-B3B0-B0C84FF9F350}" name="Name"/>
     <tableColumn id="3" xr3:uid="{A1D4EF20-200A-4B6E-A5A2-2C908927426C}" name="Hp"/>
     <tableColumn id="4" xr3:uid="{21E81982-EE18-4BE9-9C47-E7FE997BA4AD}" name="Atk"/>
@@ -520,21 +529,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330BEF0F-C7BC-4B2B-8199-B4DC333AF275}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.25" customWidth="1"/>
     <col min="2" max="2" width="9.625" customWidth="1"/>
     <col min="3" max="3" width="13.125" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="17.875" customWidth="1"/>
-    <col min="6" max="6" width="14.75" customWidth="1"/>
-    <col min="7" max="7" width="14.125" customWidth="1"/>
-    <col min="9" max="9" width="15.5" customWidth="1"/>
-    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="4" max="5" width="19.125" customWidth="1"/>
+    <col min="6" max="6" width="17.875" customWidth="1"/>
+    <col min="7" max="7" width="14.75" customWidth="1"/>
+    <col min="8" max="8" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="15.5" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -548,28 +557,31 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>18</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -584,19 +596,19 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>30</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
       </c>
       <c r="H2">
         <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -604,8 +616,11 @@
       <c r="K2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -620,28 +635,31 @@
         <v>7</v>
       </c>
       <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>50</v>
-      </c>
-      <c r="G3">
-        <v>10</v>
       </c>
       <c r="H3">
         <v>10</v>
       </c>
       <c r="I3">
+        <v>10</v>
+      </c>
+      <c r="J3">
         <v>2</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>1</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -656,94 +674,97 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>100</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>20</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>15</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>1.5</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.8</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C5" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C6" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C7" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C8" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C9" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C10" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C11" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C12" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C13" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C14" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C15" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C16" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
         <v/>

--- a/Assets/Scripts/Core/Parser/Monster.xlsx
+++ b/Assets/Scripts/Core/Parser/Monster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Desktop\Dev\IdleRPG\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0E46A8-94CE-4EC1-AC19-805265F5AF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1E8C18-98B7-4FD6-BD13-46A184144643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29190" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
+    <workbookView xWindow="3480" yWindow="2535" windowWidth="21600" windowHeight="11295" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>fileName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -121,6 +121,10 @@
   </si>
   <si>
     <t>OrcHit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkeletonHit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -596,7 +600,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
         <v>14</v>

--- a/Assets/Scripts/Core/Parser/Monster.xlsx
+++ b/Assets/Scripts/Core/Parser/Monster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Desktop\Dev\IdleRPG\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Documents\Idle_RPG_2\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1E8C18-98B7-4FD6-BD13-46A184144643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D853A82-8602-45EE-A140-AA2C81A06E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3480" yWindow="2535" windowWidth="21600" windowHeight="11295" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
+    <workbookView xWindow="5685" yWindow="1695" windowWidth="21600" windowHeight="13785" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>fileName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -125,6 +125,30 @@
   </si>
   <si>
     <t>SkeletonHit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_BANDIT_ARCHER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밴딧아처</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_BANDIT_LEADER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_BANDIT_SHIELD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밴딧리더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밴딧실드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -536,7 +560,7 @@
   <dimension ref="A1:L101"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.25" customWidth="1"/>
+    <col min="1" max="1" width="21.875" customWidth="1"/>
     <col min="2" max="2" width="9.625" customWidth="1"/>
     <col min="3" max="3" width="13.125" customWidth="1"/>
     <col min="4" max="5" width="19.125" customWidth="1"/>
@@ -545,6 +569,7 @@
     <col min="8" max="8" width="14.125" customWidth="1"/>
     <col min="10" max="10" width="15.5" customWidth="1"/>
     <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -703,21 +728,102 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C5" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
-        <v/>
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
+        <v>4294967300</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5">
+        <v>60</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C6" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
-        <v/>
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
+        <v>4294967301</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>1.5</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C7" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
-        <v/>
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
+        <v>4294967302</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7">
+        <v>80</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>0.8</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">

--- a/Assets/Scripts/Core/Parser/Monster.xlsx
+++ b/Assets/Scripts/Core/Parser/Monster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Documents\Idle_RPG_2\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D853A82-8602-45EE-A140-AA2C81A06E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095F3E89-4B2F-49F8-B6AC-FF49D86A72FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5685" yWindow="1695" windowWidth="21600" windowHeight="13785" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
+    <workbookView xWindow="5475" yWindow="1095" windowWidth="21600" windowHeight="13785" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Scripts/Core/Parser/Monster.xlsx
+++ b/Assets/Scripts/Core/Parser/Monster.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095F3E89-4B2F-49F8-B6AC-FF49D86A72FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5475" yWindow="1095" windowWidth="21600" windowHeight="13785" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Scripts/Core/Parser/Monster.xlsx
+++ b/Assets/Scripts/Core/Parser/Monster.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Documents\Idle_RPG_2\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\project-k\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095F3E89-4B2F-49F8-B6AC-FF49D86A72FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C37E931-5186-47D2-9893-D5DF965205B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>fileName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -149,6 +149,34 @@
   </si>
   <si>
     <t>밴딧실드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밴딧킹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑옷오크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오크킹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BANDIT_KING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AMORED_ORC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ORC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ORC_KING</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -827,27 +855,135 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C8" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
-        <v/>
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
+        <v>4294967303</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8">
+        <v>200</v>
+      </c>
+      <c r="H8">
+        <v>30</v>
+      </c>
+      <c r="I8">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C9" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
-        <v/>
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
+        <v>4294967304</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>15</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C10" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
-        <v/>
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
+        <v>4294967305</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10">
+        <v>80</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+      <c r="J10">
+        <v>1.5</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C11" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
-        <v/>
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
+        <v>4294967306</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11">
+        <v>300</v>
+      </c>
+      <c r="H11">
+        <v>40</v>
+      </c>
+      <c r="I11">
+        <v>50</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">

--- a/Assets/Scripts/Core/Parser/Monster.xlsx
+++ b/Assets/Scripts/Core/Parser/Monster.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\project-k\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Documents\Idle_RPG_2\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C37E931-5186-47D2-9893-D5DF965205B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095F3E89-4B2F-49F8-B6AC-FF49D86A72FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>fileName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -149,34 +149,6 @@
   </si>
   <si>
     <t>밴딧실드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>밴딧킹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>갑옷오크</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오크킹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BANDIT_KING</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AMORED_ORC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ORC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ORC_KING</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -855,135 +827,27 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
-        <v>4294967303</v>
-      </c>
-      <c r="F8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8">
-        <v>200</v>
-      </c>
-      <c r="H8">
-        <v>30</v>
-      </c>
-      <c r="I8">
-        <v>30</v>
-      </c>
-      <c r="J8">
-        <v>2</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>6</v>
+      <c r="C8" t="str">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
-        <v>4294967304</v>
-      </c>
-      <c r="F9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9">
-        <v>100</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>15</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>2</v>
+      <c r="C9" t="str">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
+        <v/>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
-        <v>4294967305</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10">
-        <v>80</v>
-      </c>
-      <c r="H10">
-        <v>7</v>
-      </c>
-      <c r="I10">
-        <v>10</v>
-      </c>
-      <c r="J10">
-        <v>1.5</v>
-      </c>
-      <c r="K10">
-        <v>2</v>
-      </c>
-      <c r="L10">
-        <v>2</v>
+      <c r="C10" t="str">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
+        <v/>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
-        <v>4294967306</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11">
-        <v>300</v>
-      </c>
-      <c r="H11">
-        <v>40</v>
-      </c>
-      <c r="I11">
-        <v>50</v>
-      </c>
-      <c r="J11">
-        <v>2</v>
-      </c>
-      <c r="K11">
-        <v>2</v>
-      </c>
-      <c r="L11">
-        <v>8</v>
+      <c r="C11" t="str">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],4294967296))</f>
+        <v/>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">

--- a/Assets/Scripts/Core/Parser/Monster.xlsx
+++ b/Assets/Scripts/Core/Parser/Monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\project-k\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C37E931-5186-47D2-9893-D5DF965205B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2982825D-DD19-4CFF-8FD7-5004618D3E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
   </bookViews>
@@ -659,7 +659,7 @@
         <v>14</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>15</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H3">
         <v>10</v>
@@ -737,7 +737,7 @@
         <v>16</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H4">
         <v>20</v>
@@ -770,7 +770,7 @@
         <v>24</v>
       </c>
       <c r="G5">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -803,7 +803,7 @@
         <v>27</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -836,7 +836,7 @@
         <v>28</v>
       </c>
       <c r="G7">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="H7">
         <v>3</v>
@@ -869,7 +869,7 @@
         <v>29</v>
       </c>
       <c r="G8">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="H8">
         <v>30</v>
@@ -902,7 +902,7 @@
         <v>30</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H9">
         <v>10</v>
@@ -935,7 +935,7 @@
         <v>16</v>
       </c>
       <c r="G10">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -968,7 +968,7 @@
         <v>31</v>
       </c>
       <c r="G11">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="H11">
         <v>40</v>

--- a/Assets/Scripts/Core/Parser/Monster.xlsx
+++ b/Assets/Scripts/Core/Parser/Monster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\project-k\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Documents\Idle_RPG_2\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2982825D-DD19-4CFF-8FD7-5004618D3E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A3F78F-5E17-4EA8-8845-2321F4155BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{96C38A8E-3BA4-4918-89A3-1A6E4E52672F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -770,10 +770,10 @@
         <v>24</v>
       </c>
       <c r="G5">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -803,10 +803,10 @@
         <v>27</v>
       </c>
       <c r="G6">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -836,7 +836,7 @@
         <v>28</v>
       </c>
       <c r="G7">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>3</v>
@@ -869,13 +869,13 @@
         <v>29</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H8">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I8">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="J8">
         <v>2</v>
@@ -902,13 +902,13 @@
         <v>30</v>
       </c>
       <c r="G9">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -935,13 +935,13 @@
         <v>16</v>
       </c>
       <c r="G10">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J10">
         <v>1.5</v>
@@ -968,13 +968,13 @@
         <v>31</v>
       </c>
       <c r="G11">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="H11">
         <v>40</v>
       </c>
       <c r="I11">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="J11">
         <v>2</v>
